--- a/sampleprojects/TaxReturn/excel/states/PA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/PA.xlsx
@@ -71,7 +71,7 @@
     <t>PA total income = AGI (simple); tax = total_income × 3.07%</t>
   </si>
   <si>
-    <t>set result.pa_total_income = the maximum of result.agi and 0.0; set result.pa_tax = result.pa_total_income * pa_tax_rate; set result.pa_state_tax = result.pa_tax; add "  PA total income: $" + result.pa_total_income to job.audit_trail; add "  PA state tax (3.07%): $" + result.pa_state_tax to job.audit_trail</t>
+    <t>set result.pa_total_income = the maximum of result.state_calc_agi and 0.0; set result.pa_tax = result.pa_total_income * pa_tax_rate; set result.pa_state_tax = result.pa_tax; add "  PA total income: $" + result.pa_total_income to job.audit_trail; add "  PA state tax (3.07%): $" + result.pa_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
